--- a/public/downloads/monthly-budget-worksheet.xlsx
+++ b/public/downloads/monthly-budget-worksheet.xlsx
@@ -1,5 +1,13 @@
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Monthly Budget" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="4">
     <font>
@@ -100,19 +108,368 @@
 </styleSheet>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheets>
-    <sheet name="Monthly Budget" sheetId="1" r:id="rId1"/>
-  </sheets>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml>﻿<?xml version="1.0" encoding="UTF-8" standalone="yes"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <cols><col min="1" max="1" width="24" customWidth="1"/><col min="2" max="2" width="16" customWidth="1"/><col min="3" max="3" width="16" customWidth="1"/><col min="4" max="4" width="14" customWidth="1"/><col min="5" max="5" width="18" customWidth="1"/><col min="6" max="6" width="30" customWidth="1"/></cols>
-  <sheetData><row r="1" ht="24" customHeight="1"><c r="A1"<c t="inlineStr" s="1"><is><t>Monthly Budget Worksheet</t></is></c>.Substring(2)<c r="B1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="C1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="D1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="E1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="F1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)</row><row r="2"><c r="A2"<c t="inlineStr" s="3"><is><t>Use planned and actual columns to spot gaps before the month gets away from you.</t></is></c>.Substring(2)<c r="B2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="C2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="D2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="E2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="F2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)</row><row r="3"><c r="A3"<c t="inlineStr" s="2"><is><t>Category</t></is></c>.Substring(2)<c r="B3"<c t="inlineStr" s="2"><is><t>Planned Amount</t></is></c>.Substring(2)<c r="C3"<c t="inlineStr" s="2"><is><t>Actual Amount</t></is></c>.Substring(2)<c r="D3"<c t="inlineStr" s="2"><is><t>Due Date</t></is></c>.Substring(2)<c r="E3"<c t="inlineStr" s="2"><is><t>Status</t></is></c>.Substring(2)<c r="F3"<c t="inlineStr" s="2"><is><t>Notes</t></is></c>.Substring(2)</row><row r="4"><c r="A4"<c t="inlineStr" s="6"><is><t>Income 1</t></is></c>.Substring(2)<c r="B4"<c s="6"><v>2500</v></c>.Substring(2)<c r="C4"<c s="6"><v>2500</v></c>.Substring(2)<c r="D4"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)<c r="E4"<c t="inlineStr" s="6"><is><t>Received</t></is></c>.Substring(2)<c r="F4"<c t="inlineStr" s="6"><is><t>Example row</t></is></c>.Substring(2)</row><row r="5"><c r="A5"<c t="inlineStr" s="6"><is><t>Income 2</t></is></c>.Substring(2)<c r="B5"<c s="6"><v>0</v></c>.Substring(2)<c r="C5"<c s="6"><v>0</v></c>.Substring(2)<c r="D5"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)<c r="E5"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)<c r="F5"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="6"><c r="A6"<c t="inlineStr" s="6"><is><t>Rent or Mortgage</t></is></c>.Substring(2)<c r="B6"<c s="6"><v>1200</v></c>.Substring(2)<c r="C6"<c s="6"><v>1200</v></c>.Substring(2)<c r="D6"<c t="inlineStr" s="6"><is><t>1st</t></is></c>.Substring(2)<c r="E6"<c t="inlineStr" s="6"><is><t>Paid</t></is></c>.Substring(2)<c r="F6"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="7"><c r="A7"<c t="inlineStr" s="6"><is><t>Utilities</t></is></c>.Substring(2)<c r="B7"<c s="6"><v>180</v></c>.Substring(2)<c r="C7"<c s="6"><v>165</v></c>.Substring(2)<c r="D7"<c t="inlineStr" s="6"><is><t>10th</t></is></c>.Substring(2)<c r="E7"<c t="inlineStr" s="6"><is><t>Paid</t></is></c>.Substring(2)<c r="F7"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="8"><c r="A8"<c t="inlineStr" s="6"><is><t>Groceries</t></is></c>.Substring(2)<c r="B8"<c s="6"><v>450</v></c>.Substring(2)<c r="C8"<c s="6"><v>425</v></c>.Substring(2)<c r="D8"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)<c r="E8"<c t="inlineStr" s="6"><is><t>In progress</t></is></c>.Substring(2)<c r="F8"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="9"><c r="A9"<c t="inlineStr" s="6"><is><t>Transportation</t></is></c>.Substring(2)<c r="B9"<c s="6"><v>250</v></c>.Substring(2)<c r="C9"<c s="6"><v>240</v></c>.Substring(2)<c r="D9"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)<c r="E9"<c t="inlineStr" s="6"><is><t>In progress</t></is></c>.Substring(2)<c r="F9"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="10"><c r="A10"<c t="inlineStr" s="6"><is><t>Debt Payments</t></is></c>.Substring(2)<c r="B10"<c s="6"><v>200</v></c>.Substring(2)<c r="C10"<c s="6"><v>200</v></c>.Substring(2)<c r="D10"<c t="inlineStr" s="6"><is><t>15th</t></is></c>.Substring(2)<c r="E10"<c t="inlineStr" s="6"><is><t>Paid</t></is></c>.Substring(2)<c r="F10"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="11"><c r="A11"<c t="inlineStr" s="6"><is><t>Savings</t></is></c>.Substring(2)<c r="B11"<c s="6"><v>100</v></c>.Substring(2)<c r="C11"<c s="6"><v>100</v></c>.Substring(2)<c r="D11"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)<c r="E11"<c t="inlineStr" s="6"><is><t>Transferred</t></is></c>.Substring(2)<c r="F11"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="12"><c r="A12"<c t="inlineStr" s="4"><is><t>Leftover</t></is></c>.Substring(2)<c r="B12"<c s="4"><f>SUM(C4:C5)-SUM(C6:C11)</f></c>.Substring(2)<c r="C12"<c t="inlineStr" s="4"><is><t></t></is></c>.Substring(2)<c r="D12"<c t="inlineStr" s="4"><is><t></t></is></c>.Substring(2)<c r="E12"<c t="inlineStr" s="4"><is><t></t></is></c>.Substring(2)<c r="F12"<c t="inlineStr" s="4"><is><t></t></is></c>.Substring(2)</row></sheetData>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>Monthly Budget Worksheet</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="3">
+        <is>
+          <t>Use planned and actual columns to spot gaps before the month gets away from you.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t>Planned Amount</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t>Actual Amount</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr" s="6">
+        <is>
+          <t>Income 1</t>
+        </is>
+      </c>
+      <c r="B4" s="6">
+        <v>2500</v>
+      </c>
+      <c r="C4" s="6">
+        <v>2500</v>
+      </c>
+      <c r="D4" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="6">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="6">
+        <is>
+          <t>Example row</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr" s="6">
+        <is>
+          <t>Income 2</t>
+        </is>
+      </c>
+      <c r="B5" s="6">
+        <v>0</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="6">
+        <is>
+          <t>Rent or Mortgage</t>
+        </is>
+      </c>
+      <c r="B6" s="6">
+        <v>1200</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1200</v>
+      </c>
+      <c r="D6" t="inlineStr" s="6">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="6">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="6">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <v>180</v>
+      </c>
+      <c r="C7" s="6">
+        <v>165</v>
+      </c>
+      <c r="D7" t="inlineStr" s="6">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="6">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="6">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="B8" s="6">
+        <v>450</v>
+      </c>
+      <c r="C8" s="6">
+        <v>425</v>
+      </c>
+      <c r="D8" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="6">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="6">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <v>250</v>
+      </c>
+      <c r="C9" s="6">
+        <v>240</v>
+      </c>
+      <c r="D9" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="6">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="6">
+        <is>
+          <t>Debt Payments</t>
+        </is>
+      </c>
+      <c r="B10" s="6">
+        <v>200</v>
+      </c>
+      <c r="C10" s="6">
+        <v>200</v>
+      </c>
+      <c r="D10" t="inlineStr" s="6">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="6">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="6">
+        <is>
+          <t>Savings</t>
+        </is>
+      </c>
+      <c r="B11" s="6">
+        <v>100</v>
+      </c>
+      <c r="C11" s="6">
+        <v>100</v>
+      </c>
+      <c r="D11" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="6">
+        <is>
+          <t>Transferred</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="4">
+        <is>
+          <t>Leftover</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>SUM(C4:C5)-SUM(C6:C11)</f>
+      </c>
+      <c r="C12" t="inlineStr" s="4">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="4">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="4">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr" s="4">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-
+</worksheet>
 </file>
--- a/public/downloads/monthly-budget-worksheet.xlsx
+++ b/public/downloads/monthly-budget-worksheet.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
   <si>
     <t>Monthly Budget Worksheet</t>
   </si>
@@ -180,15 +180,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -545,7 +548,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -579,10 +582,10 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -596,203 +599,183 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <v>2500</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="6">
         <v>2500</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <v>0</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="6">
         <v>0</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="6">
         <v>1200</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="6">
         <v>1200</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <v>180</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
         <v>165</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="6">
         <v>450</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <v>425</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="D8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="6">
         <v>250</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
         <v>240</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="6">
         <v>200</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="6">
         <v>200</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="6">
         <v>100</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="6">
         <v>100</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <f>SUM(C4:C5)-SUM(C6:C11)</f>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>7</v>
+      <c r="C12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
